--- a/spec-tech/ig/StructureDefinition-pdlgcManifestArchives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcManifestArchives.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="95">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -280,6 +280,10 @@
   </si>
   <si>
     <t>pdlgcManifestArchives.patientId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/patId
+</t>
   </si>
   <si>
     <t>Identifiant du Patient s'il s'agit d'un répertoire Patient</t>
@@ -613,7 +617,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.6796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="54.06640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1076,13 +1080,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1150,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1176,13 +1180,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1233,7 +1237,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1250,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1279,10 +1283,10 @@
         <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1333,7 +1337,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>

--- a/spec-tech/ig/StructureDefinition-pdlgcManifestArchives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcManifestArchives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgcManifestArchives.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgcManifestArchives.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
